--- a/data/tabla_desagregada_mcp_merged.xlsx
+++ b/data/tabla_desagregada_mcp_merged.xlsx
@@ -485,7 +485,7 @@
         <v>5840</v>
       </c>
       <c r="E2" t="n">
-        <v>1525</v>
+        <v>2052</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>26.11301369863014</v>
+        <v>35.13698630136987</v>
       </c>
     </row>
     <row r="3">
@@ -516,7 +516,7 @@
         <v>3000</v>
       </c>
       <c r="E3" t="n">
-        <v>1105</v>
+        <v>1393</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>36.83333333333334</v>
+        <v>46.43333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -547,7 +547,7 @@
         <v>4410</v>
       </c>
       <c r="E4" t="n">
-        <v>1199</v>
+        <v>1708</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>27.18820861678005</v>
+        <v>38.73015873015873</v>
       </c>
     </row>
     <row r="5">
@@ -578,7 +578,7 @@
         <v>5000</v>
       </c>
       <c r="E5" t="n">
-        <v>1371</v>
+        <v>1941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>27.42</v>
+        <v>38.82</v>
       </c>
     </row>
     <row r="6">
@@ -609,7 +609,7 @@
         <v>8000</v>
       </c>
       <c r="E6" t="n">
-        <v>1164</v>
+        <v>1439</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>14.55</v>
+        <v>17.9875</v>
       </c>
     </row>
     <row r="7">
@@ -640,7 +640,7 @@
         <v>5894</v>
       </c>
       <c r="E7" t="n">
-        <v>1327</v>
+        <v>1692</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>22.51442144553783</v>
+        <v>28.70715982354937</v>
       </c>
     </row>
     <row r="8">
@@ -671,7 +671,7 @@
         <v>7000</v>
       </c>
       <c r="E8" t="n">
-        <v>1195</v>
+        <v>1600</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>17.07142857142857</v>
+        <v>22.85714285714286</v>
       </c>
     </row>
     <row r="9">
@@ -702,7 +702,7 @@
         <v>4000</v>
       </c>
       <c r="E9" t="n">
-        <v>1495</v>
+        <v>1597</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>37.375</v>
+        <v>39.925</v>
       </c>
     </row>
     <row r="10">
@@ -733,7 +733,7 @@
         <v>5868</v>
       </c>
       <c r="E10" t="n">
-        <v>1255</v>
+        <v>1622</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>21.38718473074302</v>
+        <v>27.6414451261077</v>
       </c>
     </row>
     <row r="11">
@@ -764,7 +764,7 @@
         <v>5574</v>
       </c>
       <c r="E11" t="n">
-        <v>2400</v>
+        <v>2906</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>43.05705059203444</v>
+        <v>52.13491209185504</v>
       </c>
     </row>
     <row r="12">
@@ -795,7 +795,7 @@
         <v>6000</v>
       </c>
       <c r="E12" t="n">
-        <v>963</v>
+        <v>1218</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>16.05</v>
+        <v>20.3</v>
       </c>
     </row>
     <row r="13">
@@ -826,7 +826,7 @@
         <v>5000</v>
       </c>
       <c r="E13" t="n">
-        <v>1425</v>
+        <v>1802</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>28.5</v>
+        <v>36.04</v>
       </c>
     </row>
     <row r="14">
@@ -857,7 +857,7 @@
         <v>6142</v>
       </c>
       <c r="E14" t="n">
-        <v>2497</v>
+        <v>2719</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>40.65450993161836</v>
+        <v>44.26896776294367</v>
       </c>
     </row>
     <row r="15">
@@ -888,7 +888,7 @@
         <v>5025</v>
       </c>
       <c r="E15" t="n">
-        <v>1972</v>
+        <v>2556</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>39.24378109452736</v>
+        <v>50.86567164179105</v>
       </c>
     </row>
   </sheetData>

--- a/data/tabla_desagregada_mcp_merged.xlsx
+++ b/data/tabla_desagregada_mcp_merged.xlsx
@@ -485,7 +485,7 @@
         <v>5840</v>
       </c>
       <c r="E2" t="n">
-        <v>2052</v>
+        <v>2352</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>35.13698630136987</v>
+        <v>40.27397260273973</v>
       </c>
     </row>
     <row r="3">
@@ -516,7 +516,7 @@
         <v>3000</v>
       </c>
       <c r="E3" t="n">
-        <v>1393</v>
+        <v>1589</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>46.43333333333333</v>
+        <v>52.96666666666666</v>
       </c>
     </row>
     <row r="4">
@@ -547,7 +547,7 @@
         <v>4410</v>
       </c>
       <c r="E4" t="n">
-        <v>1708</v>
+        <v>1976</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>38.73015873015873</v>
+        <v>44.80725623582767</v>
       </c>
     </row>
     <row r="5">
@@ -578,7 +578,7 @@
         <v>5000</v>
       </c>
       <c r="E5" t="n">
-        <v>1941</v>
+        <v>2309</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>38.82</v>
+        <v>46.18</v>
       </c>
     </row>
     <row r="6">
@@ -609,7 +609,7 @@
         <v>8000</v>
       </c>
       <c r="E6" t="n">
-        <v>1439</v>
+        <v>1652</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>17.9875</v>
+        <v>20.65</v>
       </c>
     </row>
     <row r="7">
@@ -640,7 +640,7 @@
         <v>5894</v>
       </c>
       <c r="E7" t="n">
-        <v>1692</v>
+        <v>1899</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>28.70715982354937</v>
+        <v>32.21920597217509</v>
       </c>
     </row>
     <row r="8">
@@ -671,7 +671,7 @@
         <v>7000</v>
       </c>
       <c r="E8" t="n">
-        <v>1600</v>
+        <v>1846</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>22.85714285714286</v>
+        <v>26.37142857142857</v>
       </c>
     </row>
     <row r="9">
@@ -702,7 +702,7 @@
         <v>4000</v>
       </c>
       <c r="E9" t="n">
-        <v>1597</v>
+        <v>1699</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>39.925</v>
+        <v>42.475</v>
       </c>
     </row>
     <row r="10">
@@ -733,7 +733,7 @@
         <v>5868</v>
       </c>
       <c r="E10" t="n">
-        <v>1622</v>
+        <v>1895</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>27.6414451261077</v>
+        <v>32.29379686434901</v>
       </c>
     </row>
     <row r="11">
@@ -764,7 +764,7 @@
         <v>5574</v>
       </c>
       <c r="E11" t="n">
-        <v>2906</v>
+        <v>3153</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>52.13491209185504</v>
+        <v>56.56620021528526</v>
       </c>
     </row>
     <row r="12">
@@ -795,7 +795,7 @@
         <v>6000</v>
       </c>
       <c r="E12" t="n">
-        <v>1218</v>
+        <v>1381</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>20.3</v>
+        <v>23.01666666666667</v>
       </c>
     </row>
     <row r="13">
@@ -826,7 +826,7 @@
         <v>5000</v>
       </c>
       <c r="E13" t="n">
-        <v>1802</v>
+        <v>2033</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>36.04</v>
+        <v>40.66</v>
       </c>
     </row>
     <row r="14">
@@ -857,7 +857,7 @@
         <v>6142</v>
       </c>
       <c r="E14" t="n">
-        <v>2719</v>
+        <v>2886</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>44.26896776294367</v>
+        <v>46.98795180722892</v>
       </c>
     </row>
     <row r="15">
@@ -888,7 +888,7 @@
         <v>5025</v>
       </c>
       <c r="E15" t="n">
-        <v>2556</v>
+        <v>2959</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>50.86567164179105</v>
+        <v>58.88557213930349</v>
       </c>
     </row>
   </sheetData>

--- a/data/tabla_desagregada_mcp_merged.xlsx
+++ b/data/tabla_desagregada_mcp_merged.xlsx
@@ -485,7 +485,7 @@
         <v>5840</v>
       </c>
       <c r="E2" t="n">
-        <v>2352</v>
+        <v>2499</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>40.27397260273973</v>
+        <v>42.79109589041096</v>
       </c>
     </row>
     <row r="3">
@@ -516,7 +516,7 @@
         <v>3000</v>
       </c>
       <c r="E3" t="n">
-        <v>1589</v>
+        <v>1651</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>52.96666666666666</v>
+        <v>55.03333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -547,7 +547,7 @@
         <v>4410</v>
       </c>
       <c r="E4" t="n">
-        <v>1976</v>
+        <v>2104</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>44.80725623582767</v>
+        <v>47.70975056689342</v>
       </c>
     </row>
     <row r="5">
@@ -578,7 +578,7 @@
         <v>5000</v>
       </c>
       <c r="E5" t="n">
-        <v>2309</v>
+        <v>2329</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>46.18</v>
+        <v>46.58</v>
       </c>
     </row>
     <row r="6">
@@ -609,7 +609,7 @@
         <v>8000</v>
       </c>
       <c r="E6" t="n">
-        <v>1652</v>
+        <v>1756</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>20.65</v>
+        <v>21.95</v>
       </c>
     </row>
     <row r="7">
@@ -640,7 +640,7 @@
         <v>5894</v>
       </c>
       <c r="E7" t="n">
-        <v>1899</v>
+        <v>1997</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>32.21920597217509</v>
+        <v>33.8819138106549</v>
       </c>
     </row>
     <row r="8">
@@ -671,7 +671,7 @@
         <v>7000</v>
       </c>
       <c r="E8" t="n">
-        <v>1846</v>
+        <v>1959</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>26.37142857142857</v>
+        <v>27.98571428571429</v>
       </c>
     </row>
     <row r="9">
@@ -702,7 +702,7 @@
         <v>4000</v>
       </c>
       <c r="E9" t="n">
-        <v>1699</v>
+        <v>1788</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>42.475</v>
+        <v>44.7</v>
       </c>
     </row>
     <row r="10">
@@ -733,7 +733,7 @@
         <v>5868</v>
       </c>
       <c r="E10" t="n">
-        <v>1895</v>
+        <v>2043</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>32.29379686434901</v>
+        <v>34.8159509202454</v>
       </c>
     </row>
     <row r="11">
@@ -764,7 +764,7 @@
         <v>5574</v>
       </c>
       <c r="E11" t="n">
-        <v>3153</v>
+        <v>3370</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>56.56620021528526</v>
+        <v>60.45927520631503</v>
       </c>
     </row>
     <row r="12">
@@ -795,7 +795,7 @@
         <v>6000</v>
       </c>
       <c r="E12" t="n">
-        <v>1381</v>
+        <v>1439</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>23.01666666666667</v>
+        <v>23.98333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -826,7 +826,7 @@
         <v>5000</v>
       </c>
       <c r="E13" t="n">
-        <v>2033</v>
+        <v>2115</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>40.66</v>
+        <v>42.3</v>
       </c>
     </row>
     <row r="14">
@@ -857,7 +857,7 @@
         <v>6142</v>
       </c>
       <c r="E14" t="n">
-        <v>2886</v>
+        <v>2955</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>46.98795180722892</v>
+        <v>48.11136437642462</v>
       </c>
     </row>
     <row r="15">
@@ -888,7 +888,7 @@
         <v>5025</v>
       </c>
       <c r="E15" t="n">
-        <v>2959</v>
+        <v>3074</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>58.88557213930349</v>
+        <v>61.17412935323383</v>
       </c>
     </row>
   </sheetData>

--- a/data/tabla_desagregada_mcp_merged.xlsx
+++ b/data/tabla_desagregada_mcp_merged.xlsx
@@ -485,7 +485,7 @@
         <v>5840</v>
       </c>
       <c r="E2" t="n">
-        <v>2499</v>
+        <v>2624</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>42.79109589041096</v>
+        <v>44.93150684931507</v>
       </c>
     </row>
     <row r="3">
@@ -516,7 +516,7 @@
         <v>3000</v>
       </c>
       <c r="E3" t="n">
-        <v>1651</v>
+        <v>1703</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>55.03333333333333</v>
+        <v>56.76666666666667</v>
       </c>
     </row>
     <row r="4">
@@ -547,7 +547,7 @@
         <v>4410</v>
       </c>
       <c r="E4" t="n">
-        <v>2104</v>
+        <v>2225</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>47.70975056689342</v>
+        <v>50.45351473922902</v>
       </c>
     </row>
     <row r="5">
@@ -578,7 +578,7 @@
         <v>5000</v>
       </c>
       <c r="E5" t="n">
-        <v>2329</v>
+        <v>2431</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>46.58</v>
+        <v>48.62</v>
       </c>
     </row>
     <row r="6">
@@ -609,7 +609,7 @@
         <v>8000</v>
       </c>
       <c r="E6" t="n">
-        <v>1756</v>
+        <v>1852</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>21.95</v>
+        <v>23.15</v>
       </c>
     </row>
     <row r="7">
@@ -640,7 +640,7 @@
         <v>5894</v>
       </c>
       <c r="E7" t="n">
-        <v>1997</v>
+        <v>2015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>33.8819138106549</v>
+        <v>34.18730912792671</v>
       </c>
     </row>
     <row r="8">
@@ -671,7 +671,7 @@
         <v>7000</v>
       </c>
       <c r="E8" t="n">
-        <v>1959</v>
+        <v>2040</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>27.98571428571429</v>
+        <v>29.14285714285714</v>
       </c>
     </row>
     <row r="9">
@@ -702,7 +702,7 @@
         <v>4000</v>
       </c>
       <c r="E9" t="n">
-        <v>1788</v>
+        <v>1793</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>44.7</v>
+        <v>44.825</v>
       </c>
     </row>
     <row r="10">
@@ -733,7 +733,7 @@
         <v>5868</v>
       </c>
       <c r="E10" t="n">
-        <v>2043</v>
+        <v>2174</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>34.8159509202454</v>
+        <v>37.04839809134288</v>
       </c>
     </row>
     <row r="11">
@@ -764,7 +764,7 @@
         <v>5574</v>
       </c>
       <c r="E11" t="n">
-        <v>3370</v>
+        <v>3402</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>60.45927520631503</v>
+        <v>61.03336921420882</v>
       </c>
     </row>
     <row r="12">
@@ -795,7 +795,7 @@
         <v>6000</v>
       </c>
       <c r="E12" t="n">
-        <v>1439</v>
+        <v>1517</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>23.98333333333333</v>
+        <v>25.28333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -826,7 +826,7 @@
         <v>5000</v>
       </c>
       <c r="E13" t="n">
-        <v>2115</v>
+        <v>2161</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>42.3</v>
+        <v>43.22</v>
       </c>
     </row>
     <row r="14">
@@ -857,7 +857,7 @@
         <v>6142</v>
       </c>
       <c r="E14" t="n">
-        <v>2955</v>
+        <v>2997</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>48.11136437642462</v>
+        <v>48.79518072289157</v>
       </c>
     </row>
     <row r="15">
@@ -888,7 +888,7 @@
         <v>5025</v>
       </c>
       <c r="E15" t="n">
-        <v>3074</v>
+        <v>3232</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>61.17412935323383</v>
+        <v>64.31840796019901</v>
       </c>
     </row>
   </sheetData>

--- a/data/tabla_desagregada_mcp_merged.xlsx
+++ b/data/tabla_desagregada_mcp_merged.xlsx
@@ -613,7 +613,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Valeria Palacios</t>
+          <t>Giordano Broncano</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -768,7 +768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Carito Hernandez </t>
+          <t>Valeria Palacios</t>
         </is>
       </c>
       <c r="G11" t="n">

--- a/data/tabla_desagregada_mcp_merged.xlsx
+++ b/data/tabla_desagregada_mcp_merged.xlsx
@@ -485,7 +485,7 @@
         <v>5840</v>
       </c>
       <c r="E2" t="n">
-        <v>2624</v>
+        <v>3043</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>44.93150684931507</v>
+        <v>52.10616438356165</v>
       </c>
     </row>
     <row r="3">
@@ -516,7 +516,7 @@
         <v>3000</v>
       </c>
       <c r="E3" t="n">
-        <v>1703</v>
+        <v>1936</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>56.76666666666667</v>
+        <v>64.53333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -547,7 +547,7 @@
         <v>4410</v>
       </c>
       <c r="E4" t="n">
-        <v>2225</v>
+        <v>2572</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>50.45351473922902</v>
+        <v>58.32199546485261</v>
       </c>
     </row>
     <row r="5">
@@ -578,7 +578,7 @@
         <v>5000</v>
       </c>
       <c r="E5" t="n">
-        <v>2431</v>
+        <v>2564</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -586,7 +586,7 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>48.62</v>
+        <v>51.28</v>
       </c>
     </row>
     <row r="6">
@@ -609,7 +609,7 @@
         <v>8000</v>
       </c>
       <c r="E6" t="n">
-        <v>1852</v>
+        <v>2156</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>23.15</v>
+        <v>26.95</v>
       </c>
     </row>
     <row r="7">
@@ -640,7 +640,7 @@
         <v>5894</v>
       </c>
       <c r="E7" t="n">
-        <v>2015</v>
+        <v>2198</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>34.18730912792671</v>
+        <v>37.29216152019003</v>
       </c>
     </row>
     <row r="8">
@@ -671,7 +671,7 @@
         <v>7000</v>
       </c>
       <c r="E8" t="n">
-        <v>2040</v>
+        <v>2293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>29.14285714285714</v>
+        <v>32.75714285714286</v>
       </c>
     </row>
     <row r="9">
@@ -702,7 +702,7 @@
         <v>4000</v>
       </c>
       <c r="E9" t="n">
-        <v>1793</v>
+        <v>1809</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>44.825</v>
+        <v>45.225</v>
       </c>
     </row>
     <row r="10">
@@ -733,7 +733,7 @@
         <v>5868</v>
       </c>
       <c r="E10" t="n">
-        <v>2174</v>
+        <v>2597</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>37.04839809134288</v>
+        <v>44.25698704839809</v>
       </c>
     </row>
     <row r="11">
@@ -764,7 +764,7 @@
         <v>5574</v>
       </c>
       <c r="E11" t="n">
-        <v>3402</v>
+        <v>3480</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>61.03336921420882</v>
+        <v>62.43272335844995</v>
       </c>
     </row>
     <row r="12">
@@ -795,7 +795,7 @@
         <v>6000</v>
       </c>
       <c r="E12" t="n">
-        <v>1517</v>
+        <v>1742</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>25.28333333333333</v>
+        <v>29.03333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -826,7 +826,7 @@
         <v>5000</v>
       </c>
       <c r="E13" t="n">
-        <v>2161</v>
+        <v>2314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>43.22</v>
+        <v>46.28</v>
       </c>
     </row>
     <row r="14">
@@ -857,7 +857,7 @@
         <v>6142</v>
       </c>
       <c r="E14" t="n">
-        <v>2997</v>
+        <v>3059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>48.79518072289157</v>
+        <v>49.80462390100944</v>
       </c>
     </row>
     <row r="15">
@@ -888,7 +888,7 @@
         <v>5025</v>
       </c>
       <c r="E15" t="n">
-        <v>3232</v>
+        <v>3656</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>64.31840796019901</v>
+        <v>72.75621890547264</v>
       </c>
     </row>
   </sheetData>

--- a/data/tabla_desagregada_mcp_merged.xlsx
+++ b/data/tabla_desagregada_mcp_merged.xlsx
@@ -485,7 +485,7 @@
         <v>5840</v>
       </c>
       <c r="E2" t="n">
-        <v>3043</v>
+        <v>3083</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>52.10616438356165</v>
+        <v>52.79109589041096</v>
       </c>
     </row>
     <row r="3">
@@ -516,7 +516,7 @@
         <v>3000</v>
       </c>
       <c r="E3" t="n">
-        <v>1936</v>
+        <v>1975</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="G3" t="n">
-        <v>64.53333333333333</v>
+        <v>65.83333333333333</v>
       </c>
     </row>
     <row r="4">
@@ -547,7 +547,7 @@
         <v>4410</v>
       </c>
       <c r="E4" t="n">
-        <v>2572</v>
+        <v>2640</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="G4" t="n">
-        <v>58.32199546485261</v>
+        <v>59.8639455782313</v>
       </c>
     </row>
     <row r="5">
@@ -609,7 +609,7 @@
         <v>8000</v>
       </c>
       <c r="E6" t="n">
-        <v>2156</v>
+        <v>2245</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -617,7 +617,7 @@
         </is>
       </c>
       <c r="G6" t="n">
-        <v>26.95</v>
+        <v>28.0625</v>
       </c>
     </row>
     <row r="7">
@@ -640,7 +640,7 @@
         <v>5894</v>
       </c>
       <c r="E7" t="n">
-        <v>2198</v>
+        <v>2248</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>37.29216152019003</v>
+        <v>38.14048184594503</v>
       </c>
     </row>
     <row r="8">
@@ -671,7 +671,7 @@
         <v>7000</v>
       </c>
       <c r="E8" t="n">
-        <v>2293</v>
+        <v>2447</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -679,7 +679,7 @@
         </is>
       </c>
       <c r="G8" t="n">
-        <v>32.75714285714286</v>
+        <v>34.95714285714286</v>
       </c>
     </row>
     <row r="9">
@@ -733,7 +733,7 @@
         <v>5868</v>
       </c>
       <c r="E10" t="n">
-        <v>2597</v>
+        <v>2646</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>44.25698704839809</v>
+        <v>45.0920245398773</v>
       </c>
     </row>
     <row r="11">
@@ -764,7 +764,7 @@
         <v>5574</v>
       </c>
       <c r="E11" t="n">
-        <v>3480</v>
+        <v>3505</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>62.43272335844995</v>
+        <v>62.88123430211697</v>
       </c>
     </row>
     <row r="12">
@@ -795,7 +795,7 @@
         <v>6000</v>
       </c>
       <c r="E12" t="n">
-        <v>1742</v>
+        <v>1799</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -803,7 +803,7 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>29.03333333333333</v>
+        <v>29.98333333333333</v>
       </c>
     </row>
     <row r="13">
@@ -826,7 +826,7 @@
         <v>5000</v>
       </c>
       <c r="E13" t="n">
-        <v>2314</v>
+        <v>2368</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -834,7 +834,7 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>46.28</v>
+        <v>47.36</v>
       </c>
     </row>
     <row r="14">
@@ -857,7 +857,7 @@
         <v>6142</v>
       </c>
       <c r="E14" t="n">
-        <v>3059</v>
+        <v>3066</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -865,7 +865,7 @@
         </is>
       </c>
       <c r="G14" t="n">
-        <v>49.80462390100944</v>
+        <v>49.91859329208727</v>
       </c>
     </row>
     <row r="15">
@@ -888,7 +888,7 @@
         <v>5025</v>
       </c>
       <c r="E15" t="n">
-        <v>3656</v>
+        <v>3671</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         </is>
       </c>
       <c r="G15" t="n">
-        <v>72.75621890547264</v>
+        <v>73.05472636815921</v>
       </c>
     </row>
   </sheetData>

--- a/data/tabla_desagregada_mcp_merged.xlsx
+++ b/data/tabla_desagregada_mcp_merged.xlsx
@@ -640,7 +640,7 @@
         <v>5894</v>
       </c>
       <c r="E7" t="n">
-        <v>2248</v>
+        <v>2256</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -648,7 +648,7 @@
         </is>
       </c>
       <c r="G7" t="n">
-        <v>38.14048184594503</v>
+        <v>38.27621309806583</v>
       </c>
     </row>
     <row r="8">
@@ -733,7 +733,7 @@
         <v>5868</v>
       </c>
       <c r="E10" t="n">
-        <v>2646</v>
+        <v>2675</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -741,7 +741,7 @@
         </is>
       </c>
       <c r="G10" t="n">
-        <v>45.0920245398773</v>
+        <v>45.58623040218132</v>
       </c>
     </row>
     <row r="11">
@@ -764,7 +764,7 @@
         <v>5574</v>
       </c>
       <c r="E11" t="n">
-        <v>3505</v>
+        <v>3512</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -772,7 +772,7 @@
         </is>
       </c>
       <c r="G11" t="n">
-        <v>62.88123430211697</v>
+        <v>63.00681736634374</v>
       </c>
     </row>
     <row r="12">
